--- a/api/media/excel_files/Historical_Data.xlsx
+++ b/api/media/excel_files/Historical_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://novixconsultoria-my.sharepoint.com/personal/ctrogliero_novix_com/Documents/01 - FORECAST/Templates Base/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\matias\otros\python-excel\media\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{1CB82296-FAA9-40D6-B57C-28353001A421}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{95007507-0178-4574-8114-49A766BE71EE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="484" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7620" tabRatio="484"/>
   </bookViews>
   <sheets>
     <sheet name="Historical Data" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historical Data'!$A$1:$G$84</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Family</t>
   </si>
@@ -71,15 +70,63 @@
   <si>
     <t>Periods Per Cycle</t>
   </si>
+  <si>
+    <t>DataFamily</t>
+  </si>
+  <si>
+    <t>DataRegion</t>
+  </si>
+  <si>
+    <t>DataSalesman</t>
+  </si>
+  <si>
+    <t>DataClient</t>
+  </si>
+  <si>
+    <t>DataCategory</t>
+  </si>
+  <si>
+    <t>DataSubCategory</t>
+  </si>
+  <si>
+    <t>DataSKU</t>
+  </si>
+  <si>
+    <t>DataDescription</t>
+  </si>
+  <si>
+    <t>DataFamily2</t>
+  </si>
+  <si>
+    <t>DataRegion2</t>
+  </si>
+  <si>
+    <t>DataSalesman2</t>
+  </si>
+  <si>
+    <t>DataClient2</t>
+  </si>
+  <si>
+    <t>DataCategory2</t>
+  </si>
+  <si>
+    <t>DataSubCategory2</t>
+  </si>
+  <si>
+    <t>DataSKU2</t>
+  </si>
+  <si>
+    <t>DataDescription2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -124,6 +171,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -193,7 +248,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
@@ -209,15 +264,16 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Millares 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Millares 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Millares 2" xfId="2"/>
+    <cellStyle name="Millares 3" xfId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Normal 5" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 3" xfId="4"/>
+    <cellStyle name="Normal 4" xfId="1"/>
+    <cellStyle name="Normal 5" xfId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -596,8 +652,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:FM84"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:FO84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="12" width="15.7109375" customWidth="1"/>
@@ -606,7 +662,7 @@
     <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -801,35 +857,83 @@
       <c r="FL1" s="2"/>
       <c r="FM1" s="2"/>
     </row>
-    <row r="2" spans="1:169" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+    <row r="2" spans="1:171" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="6">
+        <v>2005</v>
+      </c>
+      <c r="J2" s="6">
+        <v>365562</v>
+      </c>
+      <c r="K2" s="6">
+        <v>5</v>
+      </c>
+      <c r="L2" s="6">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:169" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+    <row r="3" spans="1:171" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2015</v>
+      </c>
+      <c r="J3" s="6">
+        <v>36946146</v>
+      </c>
+      <c r="K3" s="6">
+        <v>7</v>
+      </c>
+      <c r="L3" s="6">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -843,7 +947,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -857,7 +961,7 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -871,7 +975,7 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -885,7 +989,7 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1056,7 +1160,7 @@
       <c r="FL8" s="3"/>
       <c r="FM8" s="3"/>
     </row>
-    <row r="9" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1227,7 +1331,7 @@
       <c r="FL9" s="3"/>
       <c r="FM9" s="3"/>
     </row>
-    <row r="10" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1397,8 +1501,9 @@
       <c r="FK10" s="3"/>
       <c r="FL10" s="3"/>
       <c r="FM10" s="3"/>
+      <c r="FO10" s="9"/>
     </row>
-    <row r="11" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1569,7 +1674,7 @@
       <c r="FL11" s="3"/>
       <c r="FM11" s="3"/>
     </row>
-    <row r="12" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1740,7 +1845,7 @@
       <c r="FL12" s="3"/>
       <c r="FM12" s="3"/>
     </row>
-    <row r="13" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -1911,7 +2016,7 @@
       <c r="FL13" s="3"/>
       <c r="FM13" s="3"/>
     </row>
-    <row r="14" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -2082,7 +2187,7 @@
       <c r="FL14" s="3"/>
       <c r="FM14" s="3"/>
     </row>
-    <row r="15" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2253,7 +2358,7 @@
       <c r="FL15" s="3"/>
       <c r="FM15" s="3"/>
     </row>
-    <row r="16" spans="1:169" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:171" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
